--- a/tables/pc_loadings_merged.xlsx
+++ b/tables/pc_loadings_merged.xlsx
@@ -47,7 +47,7 @@
     <t>pop density km2</t>
   </si>
   <si>
-    <t>motorable road nexwork</t>
+    <t>motorable road network</t>
   </si>
   <si>
     <t>amenities poi</t>
